--- a/data/trans_camb/IP25-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Provincia-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,14 +579,11 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-86,02</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-88,55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,69</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-0,68</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-87,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 16,21</t>
+          <t>-2,61; 16,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 9,05</t>
+          <t>-12,22; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-92,8; -77,89</t>
+          <t>-4,8; 13,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 12,99</t>
+          <t>-8,69; 9,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 9,13</t>
+          <t>-0,64; 11,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-94,35; -80,49</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-0,69; 12,34</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 6,39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-92,03; -81,76</t>
+          <t>-7,96; 6,2</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-0,78%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,54 +707,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 20,43</t>
+          <t>-2,74; 20,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 11,26</t>
+          <t>-13,67; 10,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,95; 16,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 16,13</t>
+          <t>-9,31; 11,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 10,83</t>
+          <t>-0,71; 14,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 15,44</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-8,17; 7,61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,8; 7,39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-87,45</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-87,96</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>6,47</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-87,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 5,49</t>
+          <t>-10,26; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,44</t>
+          <t>-1,64; 11,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-91,55; -80,44</t>
+          <t>-5,62; 8,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 8,22</t>
+          <t>2,59; 14,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 14,27</t>
+          <t>-5,44; 4,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-92,8; -82,56</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-5,49; 4,58</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2,07; 10,75</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-90,92; -83,89</t>
+          <t>2,13; 10,85</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>-0,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-0,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>7,38%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,54 +863,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 6,41</t>
+          <t>-11,29; 6,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 13,75</t>
+          <t>-1,79; 14,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,18; 9,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 9,76</t>
+          <t>3,3; 17,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 17,26</t>
+          <t>-6,02; 5,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-6,14; 5,41</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 12,75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>2,34; 12,71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-91,68</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>-9,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-9,6</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-93,74</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>-8,03</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-92,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 7,19</t>
+          <t>-7,34; 7,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 2,41</t>
+          <t>-15,84; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-95,91; -84,21</t>
+          <t>-6,09; 6,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 6,16</t>
+          <t>-18,35; -1,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -1,12</t>
+          <t>-4,64; 5,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-97,35; -88,32</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 5,26</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-14,28; -2,35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-95,63; -88,36</t>
+          <t>-14,36; -1,95</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>-10,24%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-10,24%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>-8,66%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 8,08</t>
+          <t>-7,69; 8,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 2,69</t>
+          <t>-16,7; 2,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,34; 6,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 6,8</t>
+          <t>-19,2; -1,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,56; -1,33</t>
+          <t>-4,89; 5,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-4,83; 5,79</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-14,93; -2,57</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-15,35; -2,17</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-93,55</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-91,87</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-1,53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-92,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 4,39</t>
+          <t>-10,15; 4,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 1,54</t>
+          <t>-13,98; 1,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-97,21; -86,85</t>
+          <t>-9,19; 5,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 5,38</t>
+          <t>-4,93; 8,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,66</t>
+          <t>-7,84; 2,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-96,1; -86,18</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-7,5; 3,14</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 3,09</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-95,6; -88,52</t>
+          <t>-6,19; 3,7</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-1,74%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,74%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>-2,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-2,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-1,65%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 4,68</t>
+          <t>-10,56; 4,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 1,67</t>
+          <t>-14,51; 2,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,67; 6,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 6,29</t>
+          <t>-5,11; 9,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,81</t>
+          <t>-8,23; 3,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-7,95; 3,41</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-7,66; 3,4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,58; 4,12</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-81,19</t>
+          <t>17,24</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,24</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>15,72</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-78,1</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,72</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>9,25</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-79,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 27,34</t>
+          <t>4,31; 25,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 22,29</t>
+          <t>-1,33; 23,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-90,27; -70,02</t>
+          <t>6,54; 29,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 29,69</t>
+          <t>-4,85; 21,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 21,6</t>
+          <t>7,61; 23,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-85,99; -64,85</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>8,07; 23,83</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 18,06</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-86,01; -72,22</t>
+          <t>0,61; 18,89</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>11,62%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,76; 38,46</t>
+          <t>4,87; 35,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 31,21</t>
+          <t>-1,6; 31,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,66; 44,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7,76; 44,7</t>
+          <t>-5,45; 30,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 31,39</t>
+          <t>9,05; 32,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,66; 33,16</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 24,55</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>0,79; 26,17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,37 +1383,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-92,92</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-90,5</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
           <t>0,89</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>-91,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 5,73</t>
+          <t>-11,24; 5,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 6,49</t>
+          <t>-9,69; 6,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-97,49; -85,55</t>
+          <t>-6,98; 10,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 10,42</t>
+          <t>-4,93; 11,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 11,07</t>
+          <t>-6,44; 5,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-95,64; -83,83</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 5,76</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 7,03</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-95,24; -87,18</t>
+          <t>-4,9; 6,36</t>
         </is>
       </c>
     </row>
@@ -1820,37 +1459,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>-0,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-0,15%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
           <t>0,97%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1487,39 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 6,34</t>
+          <t>-11,81; 6,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 7,18</t>
+          <t>-10,26; 7,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,39; 12,03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 12,23</t>
+          <t>-5,21; 13,3</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 13,03</t>
+          <t>-6,79; 5,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-6,14; 6,61</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 8,13</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,19; 7,2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1930,37 +1539,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-93,62</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>-3,36</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-87,93</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
           <t>0,06</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-90,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -2,64</t>
+          <t>-14,51; -1,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,24</t>
+          <t>-6,39; 3,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-96,32; -89,25</t>
+          <t>-4,58; 8,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 7,51</t>
+          <t>-4,73; 7,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,7</t>
+          <t>-7,33; 0,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-91,89; -82,82</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-7,8; 1,22</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 3,84</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-93,18; -87,4</t>
+          <t>-3,76; 4,21</t>
         </is>
       </c>
     </row>
@@ -2036,37 +1615,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>-3,71%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-3,71%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
           <t>0,06%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -2,93</t>
+          <t>-15,27; -2,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 4,58</t>
+          <t>-6,69; 3,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,11; 9,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 8,88</t>
+          <t>-5,21; 8,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 9,14</t>
+          <t>-8,04; 1,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-8,47; 1,37</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 4,4</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,08; 4,74</t>
         </is>
       </c>
     </row>
@@ -2146,37 +1695,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-90,29</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>9,97</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,97</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-83,31</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
           <t>4,82</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>-86,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,56</t>
+          <t>-6,51; 4,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,8</t>
+          <t>-5,54; 5,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-93,34; -85,93</t>
+          <t>2,55; 14,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,94; 14,07</t>
+          <t>4,81; 15,68</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,44; 15,31</t>
+          <t>-0,3; 7,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-87,29; -77,82</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 7,77</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 8,63</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-89,59; -83,6</t>
+          <t>0,98; 8,97</t>
         </is>
       </c>
     </row>
@@ -2252,37 +1771,22 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
           <t>5,56%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,25</t>
+          <t>-7,01; 4,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 5,49</t>
+          <t>-5,96; 5,9</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,95; 17,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3,41; 17,78</t>
+          <t>5,58; 19,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,04; 19,42</t>
+          <t>-0,34; 9,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 9,32</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0,84; 10,26</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1,1; 10,6</t>
         </is>
       </c>
     </row>
@@ -2362,37 +1851,22 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-90,31</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-87,54</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
           <t>1,71</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>-88,88</t>
         </is>
       </c>
     </row>
@@ -2405,47 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,47</t>
+          <t>-3,92; 1,42</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,18</t>
+          <t>-3,33; 1,96</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-91,9; -88,23</t>
+          <t>1,18; 6,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,59</t>
+          <t>1,33; 6,4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,68</t>
+          <t>-0,55; 3,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-89,27; -85,22</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 3,18</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-0,16; 3,5</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>-90,1; -87,45</t>
+          <t>-0,21; 3,52</t>
         </is>
       </c>
     </row>
@@ -2468,37 +1927,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
           <t>1,93%</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,66</t>
+          <t>-4,27; 1,6</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,46</t>
+          <t>-3,66; 2,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,33; 7,29</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,75</t>
+          <t>1,49; 7,4</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,84</t>
+          <t>-0,62; 3,7</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-0,6; 3,63</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 3,98</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,27; 3,99</t>
         </is>
       </c>
     </row>
@@ -2566,12 +1995,12 @@
   <mergeCells count="13">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A36:A39"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/IP25-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 16,05</t>
+          <t>-0,76; 16,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 8,86</t>
+          <t>-11,98; 9,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 13,63</t>
+          <t>-4,35; 13,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 9,21</t>
+          <t>-9,81; 9,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 11,97</t>
+          <t>-0,8; 12,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,2</t>
+          <t>-7,91; 6,67</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 20,45</t>
+          <t>-0,72; 21,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 10,89</t>
+          <t>-13,32; 11,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 16,69</t>
+          <t>-4,67; 16,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 11,23</t>
+          <t>-10,68; 10,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 14,59</t>
+          <t>-0,57; 15,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 7,39</t>
+          <t>-8,79; 8,01</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 5,54</t>
+          <t>-9,68; 5,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 11,83</t>
+          <t>-0,78; 11,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 8,04</t>
+          <t>-5,99; 8,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 14,41</t>
+          <t>3,08; 14,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 4,55</t>
+          <t>-5,42; 4,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 10,85</t>
+          <t>2,03; 11,14</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 6,47</t>
+          <t>-10,83; 6,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 14,11</t>
+          <t>-0,92; 13,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 9,8</t>
+          <t>-6,54; 10,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 17,55</t>
+          <t>3,36; 18,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 5,43</t>
+          <t>-6,01; 5,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 12,71</t>
+          <t>2,16; 13,18</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 7,39</t>
+          <t>-7,51; 8,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 2,15</t>
+          <t>-15,72; 2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 6,16</t>
+          <t>-6,01; 6,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,35; -1,11</t>
+          <t>-18,88; -1,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,34</t>
+          <t>-4,83; 5,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -1,95</t>
+          <t>-14,32; -1,88</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 8,36</t>
+          <t>-7,9; 9,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 2,41</t>
+          <t>-16,95; 2,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 6,82</t>
+          <t>-6,24; 7,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -1,24</t>
+          <t>-19,62; -1,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,92</t>
+          <t>-5,1; 5,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -2,17</t>
+          <t>-15,11; -2,08</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 4,0</t>
+          <t>-10,81; 4,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 1,86</t>
+          <t>-13,23; 2,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 5,62</t>
+          <t>-9,58; 5,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 8,68</t>
+          <t>-5,3; 9,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 2,84</t>
+          <t>-7,51; 3,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 3,7</t>
+          <t>-6,99; 3,55</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 4,42</t>
+          <t>-11,09; 5,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 2,09</t>
+          <t>-13,87; 2,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 6,38</t>
+          <t>-10,02; 6,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,98</t>
+          <t>-5,53; 10,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 3,24</t>
+          <t>-7,9; 3,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,12</t>
+          <t>-7,36; 3,91</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,31; 25,3</t>
+          <t>3,9; 25,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 23,1</t>
+          <t>-1,71; 21,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,54; 29,22</t>
+          <t>7,79; 31,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 21,01</t>
+          <t>-4,39; 20,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,61; 23,36</t>
+          <t>8,23; 23,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 18,89</t>
+          <t>-0,09; 18,13</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,87; 35,69</t>
+          <t>4,75; 36,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 31,92</t>
+          <t>-1,87; 31,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,66; 44,14</t>
+          <t>9,63; 48,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 30,87</t>
+          <t>-5,19; 29,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,05; 32,68</t>
+          <t>9,77; 32,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,79; 26,17</t>
+          <t>-0,05; 24,75</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 5,92</t>
+          <t>-10,4; 6,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 6,84</t>
+          <t>-10,38; 6,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 10,42</t>
+          <t>-7,68; 9,38</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 11,24</t>
+          <t>-4,15; 11,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 5,25</t>
+          <t>-6,28; 5,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 6,36</t>
+          <t>-5,13; 6,19</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 6,5</t>
+          <t>-11,04; 7,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 7,25</t>
+          <t>-11,21; 6,78</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 12,03</t>
+          <t>-8,25; 10,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 13,3</t>
+          <t>-4,41; 13,16</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 5,79</t>
+          <t>-6,58; 6,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 7,2</t>
+          <t>-5,32; 6,97</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -1,99</t>
+          <t>-14,91; -1,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,37</t>
+          <t>-6,09; 4,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 8,09</t>
+          <t>-4,97; 7,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,51</t>
+          <t>-4,86; 7,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 0,99</t>
+          <t>-7,87; 1,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,21</t>
+          <t>-4,12; 4,27</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -2,21</t>
+          <t>-15,64; -2,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 3,68</t>
+          <t>-6,45; 4,55</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,53</t>
+          <t>-5,42; 9,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 8,98</t>
+          <t>-5,25; 8,78</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,07</t>
+          <t>-8,47; 1,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 4,74</t>
+          <t>-4,43; 4,83</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,27</t>
+          <t>-5,99; 4,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 5,13</t>
+          <t>-5,72; 4,21</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,55; 14,11</t>
+          <t>2,14; 13,82</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,81; 15,68</t>
+          <t>4,63; 15,44</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,73</t>
+          <t>-0,65; 7,32</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,97</t>
+          <t>0,9; 8,59</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 4,85</t>
+          <t>-6,53; 4,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,9</t>
+          <t>-6,19; 4,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,95; 17,72</t>
+          <t>2,51; 17,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,58; 19,85</t>
+          <t>5,39; 19,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 9,24</t>
+          <t>-0,69; 8,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,6</t>
+          <t>1,02; 10,17</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,42</t>
+          <t>-3,74; 1,66</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,96</t>
+          <t>-3,02; 2,2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,28</t>
+          <t>0,97; 6,22</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,4</t>
+          <t>1,12; 6,27</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,26</t>
+          <t>-0,55; 3,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,52</t>
+          <t>0,02; 3,62</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,6</t>
+          <t>-4,13; 1,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,2</t>
+          <t>-3,28; 2,47</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,29</t>
+          <t>1,13; 7,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,4</t>
+          <t>1,29; 7,37</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,7</t>
+          <t>-0,61; 3,71</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,99</t>
+          <t>0,01; 4,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP25-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>7,18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-1,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 16,96</t>
+          <t>-4,99; 12,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 9,23</t>
+          <t>-9,48; 9,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 13,71</t>
+          <t>-1,36; 16,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 9,31</t>
+          <t>-12,2; 9,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 12,75</t>
+          <t>-0,69; 12,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 6,67</t>
+          <t>-7,33; 6,39</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>8,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-1,68%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 21,94</t>
+          <t>-5,24; 16,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 11,44</t>
+          <t>-10,26; 10,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 16,66</t>
+          <t>-1,26; 20,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 10,98</t>
+          <t>-13,23; 11,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 15,31</t>
+          <t>-0,64; 15,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 8,01</t>
+          <t>-8,17; 7,61</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,9</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,45</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>4,96</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 5,2</t>
+          <t>-5,8; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 11,29</t>
+          <t>2,54; 14,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 8,43</t>
+          <t>-9,81; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 14,78</t>
+          <t>-1,7; 11,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,82</t>
+          <t>-5,49; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,14</t>
+          <t>2,07; 10,75</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-2,8%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 6,27</t>
+          <t>-6,21; 9,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 13,65</t>
+          <t>2,83; 17,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 10,14</t>
+          <t>-10,73; 6,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,06</t>
+          <t>-1,71; 13,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,6</t>
+          <t>-6,14; 5,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 13,18</t>
+          <t>2,33; 12,75</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-9,6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-6,39</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-9,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 8,12</t>
+          <t>-6,11; 6,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 2,32</t>
+          <t>-17,65; -1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 6,96</t>
+          <t>-9,05; 7,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,88; -1,03</t>
+          <t>-15,97; 2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 5,13</t>
+          <t>-4,51; 5,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -1,88</t>
+          <t>-14,28; -2,35</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-10,24%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-6,97%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-10,24%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 9,39</t>
+          <t>-6,4; 6,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 2,5</t>
+          <t>-18,56; -1,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 7,71</t>
+          <t>-9,55; 8,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -1,16</t>
+          <t>-16,84; 2,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 5,68</t>
+          <t>-4,83; 5,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,11; -2,08</t>
+          <t>-14,93; -2,57</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-5,42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 4,53</t>
+          <t>-9,48; 5,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 2,22</t>
+          <t>-4,86; 8,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 5,35</t>
+          <t>-10,15; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 9,06</t>
+          <t>-13,72; 1,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,39</t>
+          <t>-7,5; 3,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 3,55</t>
+          <t>-7,2; 3,09</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-1,74%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-2,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-5,79%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-1,74%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 5,09</t>
+          <t>-9,94; 6,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 2,39</t>
+          <t>-5,11; 9,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 6,12</t>
+          <t>-10,63; 4,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 10,45</t>
+          <t>-14,46; 1,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 3,75</t>
+          <t>-7,95; 3,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 3,91</t>
+          <t>-7,66; 3,4</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17,24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,23</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>14,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>10,33</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17,24</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,9; 25,54</t>
+          <t>6,55; 29,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 21,62</t>
+          <t>-4,87; 21,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,79; 31,31</t>
+          <t>3,36; 27,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 20,6</t>
+          <t>-2,11; 22,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,23; 23,53</t>
+          <t>8,07; 23,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 18,13</t>
+          <t>0,16; 18,06</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22,07%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>17,37%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>12,72%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,75; 36,63</t>
+          <t>7,76; 44,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 31,02</t>
+          <t>-5,71; 31,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,63; 48,37</t>
+          <t>3,76; 38,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 29,85</t>
+          <t>-2,37; 31,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,77; 32,25</t>
+          <t>9,66; 33,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 24,75</t>
+          <t>0,2; 24,55</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1,58</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3,46</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-1,98</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-1,86</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,58</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 6,51</t>
+          <t>-6,38; 10,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 6,12</t>
+          <t>-5,0; 11,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 9,38</t>
+          <t>-11,12; 5,73</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 11,22</t>
+          <t>-11,28; 6,49</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,52</t>
+          <t>-5,7; 5,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 6,19</t>
+          <t>-4,77; 7,03</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-2,13%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-2,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 7,29</t>
+          <t>-6,79; 12,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 6,78</t>
+          <t>-5,15; 13,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 10,91</t>
+          <t>-11,61; 6,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 13,16</t>
+          <t>-11,75; 7,18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 6,23</t>
+          <t>-6,14; 6,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 6,97</t>
+          <t>-5,1; 8,13</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-8,37</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-1,34</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,91; -1,91</t>
+          <t>-4,89; 7,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 4,16</t>
+          <t>-4,76; 7,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 7,74</t>
+          <t>-14,55; -2,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 7,34</t>
+          <t>-6,22; 4,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 1,13</t>
+          <t>-7,8; 1,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 4,27</t>
+          <t>-3,75; 3,84</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-8,94%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-1,43%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -2,13</t>
+          <t>-5,37; 8,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 4,55</t>
+          <t>-5,32; 9,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 9,39</t>
+          <t>-15,38; -2,93</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 8,78</t>
+          <t>-6,59; 4,58</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 1,29</t>
+          <t>-8,47; 1,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,83</t>
+          <t>-4,05; 4,4</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>8,11</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>9,97</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-1,09</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,52</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>9,97</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 4,24</t>
+          <t>2,94; 14,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 4,21</t>
+          <t>4,44; 15,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,82</t>
+          <t>-6,25; 4,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,63; 15,44</t>
+          <t>-5,65; 4,8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,32</t>
+          <t>-0,17; 7,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,59</t>
+          <t>0,75; 8,63</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-1,2%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-0,58%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,85</t>
+          <t>3,41; 17,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 4,81</t>
+          <t>5,04; 19,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,51; 17,54</t>
+          <t>-6,73; 5,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,39; 19,32</t>
+          <t>-6,08; 5,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 8,67</t>
+          <t>-0,17; 9,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,17</t>
+          <t>0,84; 10,26</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3,79</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,48</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,66</t>
+          <t>1,28; 6,59</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,2</t>
+          <t>1,31; 6,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,22</t>
+          <t>-3,85; 1,47</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,27</t>
+          <t>-2,99; 2,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,24</t>
+          <t>-0,53; 3,18</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,62</t>
+          <t>-0,16; 3,5</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-1,36%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-0,54%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,85</t>
+          <t>1,43; 7,75</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,47</t>
+          <t>1,49; 7,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,21</t>
+          <t>-4,22; 1,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,37</t>
+          <t>-3,26; 2,46</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,71</t>
+          <t>-0,6; 3,63</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,11</t>
+          <t>-0,17; 3,98</t>
         </is>
       </c>
     </row>
